--- a/Vulnerability_Security_Test_Report.xlsx
+++ b/Vulnerability_Security_Test_Report.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-07-30 11:07:46 | Target: https://Homesh1501.github.io/SpotCart/</t>
+          <t>Execution Date: 2026-07-30 11:24:29 | Target: https://Homesh1501.github.io/SpotCart/</t>
         </is>
       </c>
     </row>
